--- a/output/pdf_financials_xlsx/SCAI.xlsx
+++ b/output/pdf_financials_xlsx/SCAI.xlsx
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.061352</v>
+        <v>-0.061352</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.066937</v>
+        <v>-0.066937</v>
       </c>
     </row>
     <row r="17">
@@ -691,10 +691,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.061352</v>
+        <v>-0.061352</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.066937</v>
+        <v>-0.066937</v>
       </c>
     </row>
     <row r="21">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.061352</v>
+        <v>-0.061352</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.066937</v>
+        <v>-0.066937</v>
       </c>
     </row>
     <row r="24">
@@ -769,10 +769,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-1.91725</v>
+        <v>1.91725</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-1.912486</v>
+        <v>1.912486</v>
       </c>
     </row>
     <row r="27">
@@ -782,10 +782,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.061352</v>
+        <v>-0.061352</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.066937</v>
+        <v>-0.066937</v>
       </c>
     </row>
     <row r="28">
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.061352</v>
+        <v>-0.061352</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.066937</v>
+        <v>-0.066937</v>
       </c>
     </row>
     <row r="30">
@@ -838,10 +838,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.1368</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1368</v>
       </c>
     </row>
     <row r="93">
@@ -2472,7 +2472,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.0988</v>
       </c>
@@ -2496,7 +2500,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
         <v>0.038</v>
       </c>
@@ -3104,10 +3112,10 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.061352</v>
+        <v>-0.061352</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.066937</v>
+        <v>-0.066937</v>
       </c>
     </row>
     <row r="34">

--- a/output/pdf_financials_xlsx/SCAI.xlsx
+++ b/output/pdf_financials_xlsx/SCAI.xlsx
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.626194</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.5683550000000001</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.626194</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.5683550000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/SCAI.xlsx
+++ b/output/pdf_financials_xlsx/SCAI.xlsx
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.002928</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.006455</v>
       </c>
     </row>
     <row r="102">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.000502</v>
+        <v>-0.002426</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.002643</v>
+        <v>0.009098</v>
       </c>
     </row>
     <row r="107">
@@ -2660,7 +2660,11 @@
           <t>HST/GST recoverable</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>-0.002928</v>
       </c>
